--- a/mapping/PDTD_DTM/Mapping_DIM_RLOS_CHANGE_TYPE.xlsx
+++ b/mapping/PDTD_DTM/Mapping_DIM_RLOS_CHANGE_TYPE.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping'!$A$5:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping'!$A$6:$E$71</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
@@ -225,7 +225,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -302,9 +302,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -355,9 +352,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -377,7 +371,7 @@
     <author>Admin</author>
   </authors>
   <commentList>
-    <comment ref="F5" authorId="0" shapeId="0">
+    <comment ref="F6" authorId="0" shapeId="0">
       <text>
         <t>Admin:
  (Chir lấy các tài khoản là tài khoản thuộc phân hệ MG, LD, AC - Thấu chi, AZ - Defer)</t>
@@ -678,13 +672,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="29.6640625" customWidth="1" style="7" min="1" max="1"/>
     <col width="20.5" customWidth="1" style="7" min="2" max="2"/>
     <col width="27.6640625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="37" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="52.1640625" customWidth="1" style="2" min="4" max="4"/>
     <col width="50.33203125" customWidth="1" style="7" min="5" max="5"/>
     <col width="48.5" customWidth="1" style="2" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="7" min="7" max="16384"/>
@@ -701,12 +695,12 @@
           <t>DIM_RLOS_CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="E1" s="43" t="inlineStr">
+      <c r="E1" s="42" t="inlineStr">
         <is>
           <t>STG_DIM_RLOS_CHANGE_TYPE AS A</t>
         </is>
       </c>
-      <c r="F1" s="43" t="n"/>
+      <c r="F1" s="42" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -719,367 +713,380 @@
           <t>Relay/merge từ STG_DTM.STG_DIM_RLOS_CHANGE_TYPE sang PDTD_DTM theo delta EFF/EXP (merge-by-key, không aggregation thêm)</t>
         </is>
       </c>
-      <c r="E2" s="43" t="n"/>
-      <c r="F2" s="43" t="n"/>
+      <c r="E2" s="42" t="n"/>
+      <c r="F2" s="42" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Primary Key</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Bao gồm các trường màu đỏ</t>
-        </is>
-      </c>
-      <c r="E3" s="43" t="n"/>
-      <c r="F3" s="43" t="n"/>
+          <t>DIMENSION_KEY</t>
+        </is>
+      </c>
+      <c r="E3" s="42" t="n"/>
+      <c r="F3" s="42" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="E4" s="43" t="n"/>
-      <c r="F4" s="43" t="n"/>
-    </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Business Key</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>CHANGE_TYPE_CODE + DETAIL_CHANGE_TYPE_CODE</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="42" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="E5" s="42" t="n"/>
+      <c r="F5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Column name</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Column type</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Item Name</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>How to mapping RLOS</t>
         </is>
       </c>
-      <c r="F5" s="25" t="n"/>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="23" t="n"/>
-      <c r="B6" s="23" t="n"/>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="F6" s="25" t="n"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
+      <c r="A7" s="23" t="n"/>
+      <c r="B7" s="23" t="n"/>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Điều kiện lấy dữ liệu</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>(A.EFF_DATE = v_batch_date OR (A.EXP_DATE &gt;= v_prev_date AND A.EXP_DATE &lt; v_batch_date))</t>
         </is>
       </c>
-      <c r="F6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="F7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Surrogate Key</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>PK — Driving: STG_DIM_RLOS_CHANGE_TYPE. Merge theo DIMENSION_KEY vào PDTD_DTM: chỉ lấy bản ghi từ STG_DTM vừa mở hiệu lực đúng v_batch_date, hoặc vừa đóng hiệu lực trong khoảng [v_prev_date, v_batch_date), rồi UPSERT theo key — không phải full reload.</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>PK — Driving: STG_DIM_RLOS_CHANGE_TYPE</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>A.DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="F7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="44" t="inlineStr">
+      <c r="F8" s="30" t="n"/>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>CHANGE_TYPE_SK</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C8" s="31" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>Khóa tham chiếu DIM_RLOS_CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Bằng đúng DIMENSION_KEY cùng dòng — dùng để Fact lookup vào DIM này. Mặc định -1 (dòng Unknown) khi lookup không khớp</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE_SK</t>
         </is>
       </c>
-      <c r="F8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="44" t="inlineStr">
+      <c r="F9" s="30" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>CHANGE_TYPE_BK</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(64)</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>Khóa nghiệp vụ hash</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Khóa nghiệp vụ hash của tổ hợp (loại thay đổi, chi tiết loại thay đổi)</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE_BK</t>
         </is>
       </c>
-      <c r="F9" s="31" t="n"/>
-    </row>
-    <row r="10" ht="17" customFormat="1" customHeight="1" s="5">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="F10" s="30" t="n"/>
+    </row>
+    <row r="11" ht="15" customFormat="1" customHeight="1" s="5">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>CHANGE_TYPE_CODE</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Mã loại thay đổi</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Business key — mã loại thay đổi điều kiện phê duyệt</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE_CODE</t>
         </is>
       </c>
-      <c r="F10" s="31" t="n"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="44" t="inlineStr">
+      <c r="F11" s="30" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>CHANGE_TYPE_NAME</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Tên loại thay đổi</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Tên loại thay đổi điều kiện phê duyệt</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE_NAME</t>
         </is>
       </c>
-      <c r="F11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="F12" s="30" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Mã chi tiết loại thay đổi</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t>Business key — mã chi tiết loại thay đổi</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t>A.DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
-      <c r="F12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="44" t="inlineStr">
+      <c r="F13" s="30" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>DETAIL_CHANGE_TYPE_NAME</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>Tên chi tiết loại thay đổi</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Tên chi tiết loại thay đổi</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>A.DETAIL_CHANGE_TYPE_NAME</t>
         </is>
       </c>
-      <c r="F13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="44" t="inlineStr">
+      <c r="F14" s="30" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>IS_ACTIVE</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>Cờ hiệu lực</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Cờ hiệu lực của loại thay đổi điều kiện phê duyệt</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>A.IS_ACTIVE</t>
         </is>
       </c>
-      <c r="F14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="44" t="inlineStr">
+      <c r="F15" s="30" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>EFF_DATE</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>Ngày hiệu lực bản ghi</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Ngày bắt đầu hiệu lực của phiên bản bản ghi (SCD Type 2)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>A.EFF_DATE</t>
         </is>
       </c>
-      <c r="F15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="44" t="inlineStr">
+      <c r="F16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>EXP_DATE</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>Ngày hết hiệu lực bản ghi</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Ngày hết hiệu lực của phiên bản bản ghi; NULL = bản ghi hiện hành</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>A.EXP_DATE</t>
         </is>
       </c>
-      <c r="F16" s="31" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1"/>
-    <row r="18" ht="68" customHeight="1"/>
-    <row r="19" ht="17" customHeight="1"/>
+      <c r="F17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1"/>
+    <row r="19" ht="68" customHeight="1"/>
     <row r="20" ht="17" customHeight="1"/>
     <row r="21" ht="17" customHeight="1"/>
     <row r="22" ht="17" customHeight="1"/>
     <row r="23" ht="17" customHeight="1"/>
     <row r="24" ht="17" customHeight="1"/>
     <row r="25" ht="17" customHeight="1"/>
-    <row r="26" ht="136" customHeight="1"/>
-    <row r="27" ht="17" customHeight="1"/>
+    <row r="26" ht="17" customHeight="1"/>
+    <row r="27" ht="136" customHeight="1"/>
     <row r="28" ht="17" customHeight="1"/>
-    <row r="29" ht="51" customHeight="1"/>
-    <row r="30" ht="17" customHeight="1"/>
+    <row r="29" ht="17" customHeight="1"/>
+    <row r="30" ht="51" customHeight="1"/>
     <row r="31" ht="17" customHeight="1"/>
     <row r="32" ht="17" customHeight="1"/>
     <row r="33" ht="17" customHeight="1"/>
@@ -1101,9 +1108,9 @@
     <row r="49" ht="17" customHeight="1"/>
     <row r="50" ht="17" customHeight="1"/>
     <row r="51" ht="17" customHeight="1"/>
-    <row r="52" ht="119" customHeight="1"/>
+    <row r="52" ht="17" customHeight="1"/>
     <row r="53" ht="119" customHeight="1"/>
-    <row r="54" ht="17" customHeight="1"/>
+    <row r="54" ht="119" customHeight="1"/>
     <row r="55" ht="17" customHeight="1"/>
     <row r="56" ht="17" customHeight="1"/>
     <row r="57" ht="17" customHeight="1"/>
@@ -1112,17 +1119,18 @@
     <row r="60" ht="17" customHeight="1"/>
     <row r="61" ht="17" customHeight="1"/>
     <row r="62" ht="17" customHeight="1"/>
-    <row r="63" ht="17" customFormat="1" customHeight="1" s="15"/>
-    <row r="64" ht="17" customHeight="1"/>
+    <row r="63" ht="17" customHeight="1"/>
+    <row r="64" ht="17" customFormat="1" customHeight="1" s="15"/>
     <row r="65" ht="17" customHeight="1"/>
     <row r="66" ht="17" customHeight="1"/>
     <row r="67" ht="17" customHeight="1"/>
     <row r="68" ht="17" customHeight="1"/>
-    <row r="69" ht="16" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="72"/>
+    <row r="69" ht="17" customHeight="1"/>
+    <row r="70" ht="16" customHeight="1"/>
+    <row r="71" ht="17" customHeight="1"/>
+    <row r="73"/>
   </sheetData>
-  <autoFilter ref="A5:E70"/>
+  <autoFilter ref="A6:E71"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>

--- a/mapping/PDTD_DTM/Mapping_DIM_RLOS_CHANGE_TYPE.xlsx
+++ b/mapping/PDTD_DTM/Mapping_DIM_RLOS_CHANGE_TYPE.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="29.6640625" customWidth="1" style="7" min="1" max="1"/>
@@ -853,27 +853,27 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="36" t="inlineStr">
         <is>
-          <t>CHANGE_TYPE_BK</t>
+          <t>CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR2(64)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ hash</t>
+          <t>Mã loại thay đổi</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ hash của tổ hợp (loại thay đổi, chi tiết loại thay đổi)</t>
+          <t>Business key — mã loại thay đổi điều kiện phê duyệt</t>
         </is>
       </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>A.CHANGE_TYPE_BK</t>
+          <t>A.CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="F10" s="30" t="n"/>
@@ -881,27 +881,27 @@
     <row r="11" ht="15" customFormat="1" customHeight="1" s="5">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>CHANGE_TYPE_CODE</t>
+          <t>CHANGE_TYPE_NAME</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>Mã loại thay đổi</t>
+          <t>Tên loại thay đổi</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>Business key — mã loại thay đổi điều kiện phê duyệt</t>
+          <t>Tên loại thay đổi điều kiện phê duyệt</t>
         </is>
       </c>
       <c r="E11" s="17" t="inlineStr">
         <is>
-          <t>A.CHANGE_TYPE_CODE</t>
+          <t>A.CHANGE_TYPE_NAME</t>
         </is>
       </c>
       <c r="F11" s="30" t="n"/>
@@ -909,27 +909,27 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>CHANGE_TYPE_NAME</t>
+          <t>DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Tên loại thay đổi</t>
+          <t>Mã chi tiết loại thay đổi</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>Tên loại thay đổi điều kiện phê duyệt</t>
+          <t>Business key — mã chi tiết loại thay đổi</t>
         </is>
       </c>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>A.CHANGE_TYPE_NAME</t>
+          <t>A.DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="F12" s="30" t="n"/>
@@ -937,27 +937,27 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>DETAIL_CHANGE_TYPE_CODE</t>
+          <t>DETAIL_CHANGE_TYPE_NAME</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>VARCHAR2(500)</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>Mã chi tiết loại thay đổi</t>
+          <t>Tên chi tiết loại thay đổi</t>
         </is>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>Business key — mã chi tiết loại thay đổi</t>
+          <t>Tên chi tiết loại thay đổi</t>
         </is>
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>A.DETAIL_CHANGE_TYPE_CODE</t>
+          <t>A.DETAIL_CHANGE_TYPE_NAME</t>
         </is>
       </c>
       <c r="F13" s="30" t="n"/>
@@ -965,27 +965,27 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="36" t="inlineStr">
         <is>
-          <t>DETAIL_CHANGE_TYPE_NAME</t>
+          <t>IS_ACTIVE</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR2(500)</t>
+          <t>VARCHAR2(1)</t>
         </is>
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>Tên chi tiết loại thay đổi</t>
+          <t>Cờ hiệu lực</t>
         </is>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>Tên chi tiết loại thay đổi</t>
+          <t>Cờ hiệu lực của loại thay đổi điều kiện phê duyệt</t>
         </is>
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>A.DETAIL_CHANGE_TYPE_NAME</t>
+          <t>A.IS_ACTIVE</t>
         </is>
       </c>
       <c r="F14" s="30" t="n"/>
@@ -993,27 +993,27 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>IS_ACTIVE</t>
+          <t>EFF_DATE</t>
         </is>
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>VARCHAR2(1)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>Cờ hiệu lực</t>
+          <t>Ngày hiệu lực bản ghi</t>
         </is>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>Cờ hiệu lực của loại thay đổi điều kiện phê duyệt</t>
+          <t>Ngày bắt đầu hiệu lực của phiên bản bản ghi (SCD Type 2)</t>
         </is>
       </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>A.IS_ACTIVE</t>
+          <t>A.EFF_DATE</t>
         </is>
       </c>
       <c r="F15" s="30" t="n"/>
@@ -1021,7 +1021,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="36" t="inlineStr">
         <is>
-          <t>EFF_DATE</t>
+          <t>EXP_DATE</t>
         </is>
       </c>
       <c r="B16" s="26" t="inlineStr">
@@ -1031,49 +1031,22 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>Ngày hiệu lực bản ghi</t>
+          <t>Ngày hết hiệu lực bản ghi</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>Ngày bắt đầu hiệu lực của phiên bản bản ghi (SCD Type 2)</t>
+          <t>Ngày hết hiệu lực của phiên bản bản ghi; NULL = bản ghi hiện hành</t>
         </is>
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>A.EFF_DATE</t>
+          <t>A.EXP_DATE</t>
         </is>
       </c>
       <c r="F16" s="30" t="n"/>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="36" t="inlineStr">
-        <is>
-          <t>EXP_DATE</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>Ngày hết hiệu lực bản ghi</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>Ngày hết hiệu lực của phiên bản bản ghi; NULL = bản ghi hiện hành</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>A.EXP_DATE</t>
-        </is>
-      </c>
-      <c r="F17" s="30" t="n"/>
-    </row>
+    <row r="17" ht="30" customHeight="1"/>
     <row r="18" ht="17" customHeight="1"/>
     <row r="19" ht="68" customHeight="1"/>
     <row r="20" ht="17" customHeight="1"/>
@@ -1128,7 +1101,6 @@
     <row r="69" ht="17" customHeight="1"/>
     <row r="70" ht="16" customHeight="1"/>
     <row r="71" ht="17" customHeight="1"/>
-    <row r="73"/>
   </sheetData>
   <autoFilter ref="A6:E71"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
